--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,8 +1346,7 @@
     <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
   </si>
   <si>
-    <t>Dental.DeviceTracking.PatientIEN
-Dental.DeviceTrackingDetail.PatientIEN</t>
+    <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTrackingDetail.PatientIEN</t>
   </si>
   <si>
     <t>Device.owner</t>
@@ -1815,7 +1814,7 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="99.88671875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="68.8828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
   </si>
   <si>
     <t>Mapping: UDI Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -628,10 +628,10 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1352: source value from DENTAL DEVICE TRACKING - IEN (#228.9-.001)</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1352: source value from DENTAL DEVICE TRACKING - IEN (#228.9-.001)</t>
   </si>
   <si>
     <t>Device.identifier.period</t>
@@ -743,6 +743,12 @@
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
   </si>
   <si>
+    <t>1354: source value from DENTAL DEVICE TRACKING - UDI (#228.9-1)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DeviceIdentification</t>
+  </si>
+  <si>
     <t>Role.id.extension</t>
   </si>
   <si>
@@ -750,12 +756,6 @@
   </si>
   <si>
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
-  </si>
-  <si>
-    <t>1354: source value from DENTAL DEVICE TRACKING - UDI (#228.9-1)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DeviceIdentification</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -886,16 +886,16 @@
     <t>http://va.gov/fhir/ValueSet/VSVFDentalDeviceStatus</t>
   </si>
   <si>
+    <t>1362: terminologyMaps using VF_DentalDeviceStatus on DENTAL DEVICE TRACKING - STATUS (#228.9-.08)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DeviceStatus</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1362: terminologyMaps using VF_DentalDeviceStatus on DENTAL DEVICE TRACKING - STATUS (#228.9-.08)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DeviceStatus</t>
   </si>
   <si>
     <t>Device.statusReason</t>
@@ -929,18 +929,18 @@
     <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
+    <t>1364: source value from DENTAL DEVICE TRACKING - DONATION ID (#228.9-4.8)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DonationIdentification</t>
+  </si>
+  <si>
     <t>.lotNumberText</t>
   </si>
   <si>
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
   </si>
   <si>
-    <t>1364: source value from DENTAL DEVICE TRACKING - DONATION ID (#228.9-4.8)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DonationIdentification</t>
-  </si>
-  <si>
     <t>Device.manufacturer</t>
   </si>
   <si>
@@ -950,13 +950,13 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
+    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (#228.9-4.1)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DeviceManufacturer</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
-  </si>
-  <si>
-    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (#228.9-4.1)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DeviceManufacturer</t>
   </si>
   <si>
     <t>Device.manufactureDate</t>
@@ -972,18 +972,18 @@
     <t>The date and time when the device was manufactured.</t>
   </si>
   <si>
+    <t>1372: source value from DENTAL DEVICE TRACKING - MANUFACTURER DATE (#228.9-4.6)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.ManufacturerDate</t>
+  </si>
+  <si>
     <t>.existenceTime.low</t>
   </si>
   <si>
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
-    <t>1372: source value from DENTAL DEVICE TRACKING - MANUFACTURER DATE (#228.9-4.6)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.ManufacturerDate</t>
-  </si>
-  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -993,18 +993,18 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
+    <t>1375: source value from DENTAL DEVICE TRACKING - EXPRATION DATE (#228.9-4.7)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.ExpirationDate</t>
+  </si>
+  <si>
     <t>.expirationTime</t>
   </si>
   <si>
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
-    <t>1375: source value from DENTAL DEVICE TRACKING - EXPRATION DATE (#228.9-4.7)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.ExpirationDate</t>
-  </si>
-  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -1032,13 +1032,13 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
+    <t>1384: source value from DENTAL DEVICE TRACKING - S/N (#228.9-4.3)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.SerialNumber</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].id</t>
-  </si>
-  <si>
-    <t>1384: source value from DENTAL DEVICE TRACKING - S/N (#228.9-4.3)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.SerialNumber</t>
   </si>
   <si>
     <t>Device.deviceName</t>
@@ -1100,13 +1100,13 @@
     <t>The model number for the device.</t>
   </si>
   <si>
+    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (#228.9-4.2)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DeviceModel</t>
+  </si>
+  <si>
     <t>.softwareName (included as part)</t>
-  </si>
-  <si>
-    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (#228.9-4.2)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DeviceModel</t>
   </si>
   <si>
     <t>Device.partNumber</t>
@@ -1182,13 +1182,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (#228.9-2)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.DeviceType</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (#228.9-2)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.DeviceType</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1337,16 +1337,16 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
+    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
+  </si>
+  <si>
+    <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTrackingDetail.PatientIEN</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
-  </si>
-  <si>
-    <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTrackingDetail.PatientIEN</t>
   </si>
   <si>
     <t>Device.owner</t>
@@ -1810,11 +1810,11 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="99.88671875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="68.8828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.88671875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="68.8828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2044,13 +2044,13 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>78</v>
@@ -2627,13 +2627,13 @@
         <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2744,13 +2744,13 @@
         <v>78</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2861,13 +2861,13 @@
         <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2980,13 +2980,13 @@
         <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -3097,19 +3097,19 @@
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3212,13 +3212,13 @@
         <v>78</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -3329,13 +3329,13 @@
         <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3448,13 +3448,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3567,13 +3567,13 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3686,13 +3686,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3809,10 +3809,10 @@
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -3918,13 +3918,13 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4035,13 +4035,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4267,16 +4267,16 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
@@ -4382,13 +4382,13 @@
         <v>78</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4499,13 +4499,13 @@
         <v>137</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4618,13 +4618,13 @@
         <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4848,19 +4848,19 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4965,13 +4965,13 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5082,19 +5082,19 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5199,19 +5199,19 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5316,13 +5316,13 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5437,13 +5437,13 @@
         <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>78</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5549,13 +5549,13 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>275</v>
+        <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5666,13 +5666,13 @@
         <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>291</v>
@@ -5781,16 +5781,16 @@
         <v>295</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5896,13 +5896,13 @@
         <v>302</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>305</v>
@@ -6011,13 +6011,13 @@
         <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>311</v>
+        <v>236</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>312</v>
@@ -6123,19 +6123,19 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>316</v>
+        <v>236</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>317</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6243,16 +6243,16 @@
         <v>322</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>236</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6470,13 +6470,13 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6587,13 +6587,13 @@
         <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6706,13 +6706,13 @@
         <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6936,16 +6936,16 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7054,16 +7054,16 @@
         <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>345</v>
+        <v>236</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7168,16 +7168,16 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>322</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7398,13 +7398,13 @@
         <v>78</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7515,13 +7515,13 @@
         <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7634,13 +7634,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7756,16 +7756,16 @@
         <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7983,13 +7983,13 @@
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8100,13 +8100,13 @@
         <v>137</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8219,13 +8219,13 @@
         <v>137</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8452,13 +8452,13 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8679,13 +8679,13 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8796,13 +8796,13 @@
         <v>137</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8915,13 +8915,13 @@
         <v>137</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9148,13 +9148,13 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9490,13 +9490,13 @@
         <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9607,13 +9607,13 @@
         <v>137</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9726,13 +9726,13 @@
         <v>137</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10194,13 +10194,13 @@
         <v>423</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>425</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10303,16 +10303,16 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10420,16 +10420,16 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10537,16 +10537,16 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10654,16 +10654,16 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10769,13 +10769,13 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10884,13 +10884,13 @@
         <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -743,7 +743,7 @@
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
   </si>
   <si>
-    <t>1354: source value from DENTAL DEVICE TRACKING - UDI (#228.9-1)</t>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceIdentification</t>
@@ -886,7 +886,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFDentalDeviceStatus</t>
   </si>
   <si>
-    <t>1362: terminologyMaps using VF_DentalDeviceStatus on DENTAL DEVICE TRACKING - STATUS (#228.9-.08)</t>
+    <t>1355: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceStatus</t>
@@ -929,7 +929,7 @@
     <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
-    <t>1364: source value from DENTAL DEVICE TRACKING - DONATION ID (#228.9-4.8)</t>
+    <t>1363: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DonationIdentification</t>
@@ -972,7 +972,7 @@
     <t>The date and time when the device was manufactured.</t>
   </si>
   <si>
-    <t>1372: source value from DENTAL DEVICE TRACKING - MANUFACTURER DATE (#228.9-4.6)</t>
+    <t>1371: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.ManufacturerDate</t>
@@ -993,7 +993,7 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
-    <t>1375: source value from DENTAL DEVICE TRACKING - EXPRATION DATE (#228.9-4.7)</t>
+    <t>1374: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.ExpirationDate</t>
@@ -1014,7 +1014,7 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
-    <t>1378: source value from DENTAL DEVICE TRACKING - LOT (#228.9-4.4)</t>
+    <t>1377: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceLotNumber</t>
@@ -1032,7 +1032,7 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
-    <t>1384: source value from DENTAL DEVICE TRACKING - S/N (#228.9-4.3)</t>
+    <t>1381: target not supported</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.SerialNumber</t>
@@ -1048,6 +1048,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -1810,7 +1813,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.88671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="68.8828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6355,7 +6358,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6372,10 +6375,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6487,10 +6490,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6604,10 +6607,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6723,14 +6726,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6752,10 +6755,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6806,7 +6809,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6838,10 +6841,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6867,10 +6870,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6900,10 +6903,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6921,7 +6924,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6942,7 +6945,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>236</v>
@@ -6953,10 +6956,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6982,10 +6985,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7036,7 +7039,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7051,13 +7054,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>236</v>
@@ -7068,10 +7071,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7097,10 +7100,10 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>321</v>
@@ -7153,7 +7156,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7185,10 +7188,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7214,10 +7217,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7247,10 +7250,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7268,7 +7271,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7300,10 +7303,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7415,10 +7418,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7532,10 +7535,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7558,19 +7561,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7619,7 +7622,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7640,7 +7643,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7651,10 +7654,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7680,16 +7683,16 @@
         <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7738,7 +7741,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7753,13 +7756,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7770,10 +7773,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7799,10 +7802,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7853,7 +7856,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7885,10 +7888,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8000,10 +8003,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8117,10 +8120,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8236,14 +8239,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8265,10 +8268,10 @@
         <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8319,7 +8322,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8351,10 +8354,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8380,10 +8383,10 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8434,7 +8437,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8466,10 +8469,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8495,10 +8498,10 @@
         <v>217</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8549,7 +8552,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8581,10 +8584,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8696,10 +8699,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8813,10 +8816,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8932,14 +8935,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8961,10 +8964,10 @@
         <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9015,7 +9018,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9047,10 +9050,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9076,10 +9079,10 @@
         <v>144</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9130,7 +9133,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9162,10 +9165,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9191,10 +9194,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9245,7 +9248,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>86</v>
@@ -9277,10 +9280,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9306,10 +9309,10 @@
         <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9360,7 +9363,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9392,10 +9395,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9507,10 +9510,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9624,10 +9627,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9743,10 +9746,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9772,10 +9775,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9826,7 +9829,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>86</v>
@@ -9858,10 +9861,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9884,13 +9887,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9941,7 +9944,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9973,10 +9976,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10002,10 +10005,10 @@
         <v>174</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10056,7 +10059,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10088,10 +10091,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10114,17 +10117,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10173,7 +10176,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10188,16 +10191,16 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10205,10 +10208,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10234,10 +10237,10 @@
         <v>206</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10288,7 +10291,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10309,10 +10312,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10320,10 +10323,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10346,16 +10349,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10405,7 +10408,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10426,10 +10429,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10437,10 +10440,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10463,17 +10466,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10522,7 +10525,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10543,10 +10546,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10554,10 +10557,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10583,13 +10586,13 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10639,7 +10642,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10660,10 +10663,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10671,10 +10674,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10697,13 +10700,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10754,7 +10757,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10775,7 +10778,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10786,10 +10789,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10815,10 +10818,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10869,7 +10872,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10901,10 +10904,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10927,13 +10930,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10984,7 +10987,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -845,6 +845,9 @@
   </si>
   <si>
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+  </si>
+  <si>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>
@@ -5202,7 +5205,7 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
@@ -5214,15 +5217,15 @@
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5248,14 +5251,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5283,10 +5286,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5304,7 +5307,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5325,7 +5328,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5336,10 +5339,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5365,13 +5368,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5401,7 +5404,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5419,7 +5422,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5434,16 +5437,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5451,10 +5454,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5480,10 +5483,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5513,10 +5516,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5534,7 +5537,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5558,7 +5561,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5566,14 +5569,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5595,13 +5598,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5651,7 +5654,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5666,27 +5669,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>236</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5712,10 +5715,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5766,7 +5769,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5781,13 +5784,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>236</v>
@@ -5798,10 +5801,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5824,13 +5827,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5881,7 +5884,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5896,27 +5899,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>236</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5939,13 +5942,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5996,7 +5999,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6011,27 +6014,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>236</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6057,10 +6060,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6111,7 +6114,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6126,27 +6129,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>236</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6172,13 +6175,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6228,7 +6231,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6243,13 +6246,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>236</v>
@@ -6260,10 +6263,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6289,10 +6292,10 @@
         <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6343,7 +6346,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6358,7 +6361,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6375,10 +6378,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6490,10 +6493,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6607,10 +6610,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6726,14 +6729,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6755,10 +6758,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6809,7 +6812,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6841,10 +6844,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6870,10 +6873,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6903,10 +6906,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6924,7 +6927,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6945,7 +6948,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>236</v>
@@ -6956,10 +6959,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6985,10 +6988,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7039,7 +7042,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7054,13 +7057,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>236</v>
@@ -7071,10 +7074,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7100,13 +7103,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7156,7 +7159,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7177,7 +7180,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>236</v>
@@ -7188,10 +7191,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7217,10 +7220,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7250,10 +7253,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7271,7 +7274,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7303,10 +7306,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7418,10 +7421,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7535,10 +7538,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7561,19 +7564,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7622,7 +7625,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7643,7 +7646,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7654,10 +7657,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7683,16 +7686,16 @@
         <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7741,7 +7744,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7756,13 +7759,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7773,10 +7776,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7802,10 +7805,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7856,7 +7859,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7888,10 +7891,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8003,10 +8006,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8120,10 +8123,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8239,14 +8242,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8268,10 +8271,10 @@
         <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8322,7 +8325,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8354,10 +8357,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8383,10 +8386,10 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8437,7 +8440,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8469,10 +8472,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8498,10 +8501,10 @@
         <v>217</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8552,7 +8555,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8584,10 +8587,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8699,10 +8702,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8816,10 +8819,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8935,14 +8938,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8964,10 +8967,10 @@
         <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9018,7 +9021,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9050,10 +9053,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9079,10 +9082,10 @@
         <v>144</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9133,7 +9136,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9165,10 +9168,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9194,10 +9197,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9248,7 +9251,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>86</v>
@@ -9280,10 +9283,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9309,10 +9312,10 @@
         <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9363,7 +9366,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9395,10 +9398,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9510,10 +9513,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9627,10 +9630,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9746,10 +9749,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9775,10 +9778,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9829,7 +9832,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>86</v>
@@ -9861,10 +9864,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9887,13 +9890,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9944,7 +9947,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9976,10 +9979,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10005,10 +10008,10 @@
         <v>174</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10059,7 +10062,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10091,10 +10094,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10117,17 +10120,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10176,7 +10179,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10191,16 +10194,16 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10208,10 +10211,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10237,10 +10240,10 @@
         <v>206</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10291,7 +10294,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10312,10 +10315,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10323,10 +10326,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10349,16 +10352,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10408,7 +10411,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10429,10 +10432,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10440,10 +10443,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10466,17 +10469,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10525,7 +10528,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10546,10 +10549,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10557,10 +10560,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10586,13 +10589,13 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10642,7 +10645,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10663,10 +10666,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10674,10 +10677,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10700,13 +10703,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10757,7 +10760,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10778,7 +10781,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10789,10 +10792,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10818,10 +10821,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10872,7 +10875,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10893,7 +10896,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10904,10 +10907,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10930,13 +10933,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10987,7 +10990,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -847,7 +847,7 @@
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
   </si>
   <si>
-    <t>1794: target not supported</t>
+    <t>1795: target not supported</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file DENTAL DEVICE TRACKING (#228.9) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file DENTAL DEVICE TRACKING (228.9) to us-core-implantable-device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -628,7 +628,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1352: source value from DENTAL DEVICE TRACKING - IEN (#228.9-.001)</t>
+    <t>1352: source value from DENTAL DEVICE TRACKING - IEN (228.9-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -953,7 +953,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (#228.9-4.1)</t>
+    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (228.9-4.1)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceManufacturer</t>
@@ -1106,7 +1106,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (#228.9-4.2)</t>
+    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (228.9-4.2)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceModel</t>
@@ -1188,7 +1188,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (#228.9-2)</t>
+    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (228.9-2)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceType</t>
@@ -1343,7 +1343,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (#228.9-.03)</t>
+    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (228.9-.03)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTrackingDetail.PatientIEN</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1346,7 +1346,7 @@
     <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (228.9-.03)</t>
   </si>
   <si>
-    <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTrackingDetail.PatientIEN</t>
+    <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTracking.PatientSID,Dental.DeviceTrackingDetail.PatientIEN</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
@@ -1817,7 +1817,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="68.8828125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="100.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,10 +601,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1352-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -1164,7 +1170,17 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;code value="277986000"/&gt;
+  &lt;display value="Dental equipment and devices"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>1398-1: fixed value = http://snomed.info/sct#277986000 Dental equipment and devices</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
@@ -3607,7 +3623,7 @@
         <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
@@ -3638,10 +3654,10 @@
         <v>78</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>78</v>
@@ -3677,7 +3693,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3692,13 +3708,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3709,10 +3725,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3738,13 +3754,13 @@
         <v>152</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3758,7 +3774,7 @@
         <v>78</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>78</v>
@@ -3794,7 +3810,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3809,13 +3825,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3826,10 +3842,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3852,13 +3868,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3909,7 +3925,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3930,7 +3946,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3941,10 +3957,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3967,16 +3983,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4026,7 +4042,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4047,7 +4063,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4058,10 +4074,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4084,13 +4100,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4141,7 +4157,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4173,10 +4189,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4199,16 +4215,16 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4258,7 +4274,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4279,7 +4295,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>149</v>
@@ -4290,10 +4306,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4405,10 +4421,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4522,14 +4538,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4551,10 +4567,10 @@
         <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>135</v>
@@ -4609,7 +4625,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4641,14 +4657,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4670,10 +4686,10 @@
         <v>152</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4724,7 +4740,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4739,31 +4755,31 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4785,10 +4801,10 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4839,7 +4855,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4860,21 +4876,21 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4900,14 +4916,14 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4956,7 +4972,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4977,7 +4993,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4988,14 +5004,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5014,16 +5030,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5073,7 +5089,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5094,25 +5110,25 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5134,13 +5150,13 @@
         <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5190,7 +5206,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5205,27 +5221,27 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5251,14 +5267,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5286,10 +5302,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5307,7 +5323,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5328,7 +5344,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5339,10 +5355,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5368,13 +5384,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5404,7 +5420,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5422,7 +5438,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5437,16 +5453,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5454,10 +5470,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5483,10 +5499,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5516,10 +5532,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5537,7 +5553,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5561,7 +5577,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5569,14 +5585,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5598,13 +5614,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5654,7 +5670,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5669,27 +5685,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5715,10 +5731,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5769,7 +5785,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5784,16 +5800,16 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>129</v>
@@ -5801,10 +5817,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5827,13 +5843,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5884,7 +5900,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5899,27 +5915,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5942,13 +5958,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5999,7 +6015,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6014,27 +6030,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6060,10 +6076,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6114,7 +6130,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6129,27 +6145,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6175,13 +6191,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6231,7 +6247,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6246,16 +6262,16 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6263,10 +6279,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6289,13 +6305,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6346,7 +6362,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6361,7 +6377,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6378,10 +6394,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6493,10 +6509,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6610,14 +6626,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6639,10 +6655,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>135</v>
@@ -6697,7 +6713,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6729,14 +6745,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6758,10 +6774,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6812,7 +6828,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6844,10 +6860,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6873,10 +6889,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6906,10 +6922,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6927,7 +6943,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6948,10 +6964,10 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6959,10 +6975,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6988,10 +7004,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7042,7 +7058,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7057,16 +7073,16 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7074,10 +7090,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7103,13 +7119,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7159,7 +7175,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7180,10 +7196,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7191,10 +7207,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7220,10 +7236,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7253,10 +7269,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7274,7 +7290,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7306,10 +7322,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7421,10 +7437,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7538,10 +7554,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7555,7 +7571,7 @@
         <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -7564,19 +7580,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7586,7 +7602,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -7625,7 +7641,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7640,13 +7656,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7657,10 +7673,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7686,16 +7702,16 @@
         <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7744,7 +7760,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7759,13 +7775,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7776,10 +7792,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7802,13 +7818,13 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7859,7 +7875,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7891,10 +7907,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8006,10 +8022,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8123,14 +8139,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8152,10 +8168,10 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>135</v>
@@ -8210,7 +8226,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8242,14 +8258,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8271,10 +8287,10 @@
         <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8325,7 +8341,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8357,10 +8373,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8386,10 +8402,10 @@
         <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8440,7 +8456,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8464,7 +8480,7 @@
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8472,10 +8488,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8498,13 +8514,13 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8555,7 +8571,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8587,10 +8603,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8702,10 +8718,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8819,14 +8835,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8848,10 +8864,10 @@
         <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>135</v>
@@ -8906,7 +8922,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8938,14 +8954,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8967,10 +8983,10 @@
         <v>174</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9021,7 +9037,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9053,10 +9069,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9082,10 +9098,10 @@
         <v>144</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9136,7 +9152,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9160,7 +9176,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9168,10 +9184,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9197,10 +9213,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9251,7 +9267,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>86</v>
@@ -9283,10 +9299,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9309,13 +9325,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9366,7 +9382,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9398,10 +9414,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9513,10 +9529,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9630,14 +9646,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9659,10 +9675,10 @@
         <v>132</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>135</v>
@@ -9717,7 +9733,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9749,10 +9765,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9778,10 +9794,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9832,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>86</v>
@@ -9864,10 +9880,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9890,13 +9906,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9947,7 +9963,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9979,10 +9995,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10008,10 +10024,10 @@
         <v>174</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10062,7 +10078,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10094,10 +10110,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10120,17 +10136,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10179,7 +10195,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10194,16 +10210,16 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10211,10 +10227,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10237,13 +10253,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10294,7 +10310,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10315,10 +10331,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10326,10 +10342,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10352,16 +10368,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10411,7 +10427,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10432,10 +10448,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10443,10 +10459,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10469,17 +10485,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10528,7 +10544,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10549,10 +10565,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10560,10 +10576,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10589,13 +10605,13 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10645,7 +10661,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10666,10 +10682,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10677,10 +10693,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10703,13 +10719,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10760,7 +10776,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10781,7 +10797,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10792,10 +10808,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10821,10 +10837,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10875,7 +10891,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10896,7 +10912,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10907,10 +10923,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10933,13 +10949,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10990,7 +11006,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/228.9</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1352-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1352-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/228.9</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/228.9</t>
+    <t>http://va.gov/identifiers/$Sta3n/228.9</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1352-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/228.9</t>
+    <t>1352-1: fixed value = http://va.gov/identifiers/$Sta3n/228.9</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3197" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1170,20 +1170,134 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;code value="277986000"/&gt;
-  &lt;display value="Dental equipment and devices"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1398-1: fixed value = http://snomed.info/sct#277986000 Dental equipment and devices</t>
-  </si>
-  <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Device.type.coding.id</t>
+  </si>
+  <si>
+    <t>Device.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Device.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1398-1: fixed value = http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Device.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Device.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>277986000</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1398-2: fixed value = #277986000</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Device.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Dental equipment and devices</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1398-3: fixed value = Dental equipment and devices</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Device.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Device.type.text</t>
@@ -1794,7 +1908,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AO86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
@@ -7571,7 +7685,7 @@
         <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -7602,46 +7716,46 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7656,13 +7770,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7673,10 +7787,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7690,29 +7804,25 @@
         <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>152</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>372</v>
+        <v>153</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7760,7 +7870,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>155</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7772,16 +7882,16 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>377</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7792,14 +7902,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7818,15 +7928,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>219</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>381</v>
+        <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7863,19 +7975,19 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>380</v>
+        <v>162</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7887,7 +7999,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7896,7 +8008,7 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7907,10 +8019,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7924,25 +8036,29 @@
         <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>153</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7951,7 +8067,7 @@
         <v>78</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>78</v>
+        <v>376</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>78</v>
@@ -7990,7 +8106,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>155</v>
+        <v>377</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8002,16 +8118,16 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>156</v>
+        <v>379</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8022,21 +8138,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8045,19 +8161,19 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>133</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>158</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>135</v>
+        <v>383</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8107,19 +8223,19 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8128,7 +8244,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>156</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8139,45 +8255,43 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>228</v>
+        <v>387</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>141</v>
+        <v>389</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8187,7 +8301,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -8226,28 +8340,28 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>230</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>129</v>
+        <v>393</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8258,42 +8372,44 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>336</v>
+        <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8302,7 +8418,7 @@
         <v>78</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>78</v>
@@ -8341,10 +8457,10 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>86</v>
@@ -8356,13 +8472,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8373,10 +8489,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8396,19 +8512,23 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8456,7 +8576,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8477,10 +8597,10 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8488,10 +8608,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8502,28 +8622,32 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8571,13 +8695,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8586,13 +8710,13 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8727,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8617,7 +8741,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8629,13 +8753,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>153</v>
+        <v>420</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>154</v>
+        <v>421</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8686,19 +8810,19 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>155</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8707,7 +8831,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8718,21 +8842,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8744,17 +8868,15 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8803,19 +8925,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8835,14 +8957,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8855,26 +8977,24 @@
         <v>78</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="O61" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8922,7 +9042,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8943,7 +9063,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8954,42 +9074,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>399</v>
+        <v>228</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9037,19 +9161,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>230</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9058,7 +9182,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9069,18 +9193,18 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>86</v>
@@ -9095,13 +9219,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9152,10 +9276,10 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>86</v>
@@ -9176,7 +9300,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9184,10 +9308,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9195,7 +9319,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>86</v>
@@ -9213,10 +9337,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9267,10 +9391,10 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>86</v>
@@ -9291,7 +9415,7 @@
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9299,10 +9423,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9328,10 +9452,10 @@
         <v>219</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9382,7 +9506,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9414,10 +9538,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9529,10 +9653,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9646,10 +9770,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9765,18 +9889,18 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>86</v>
@@ -9794,10 +9918,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9848,10 +9972,10 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>86</v>
@@ -9880,10 +10004,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9894,7 +10018,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -9906,13 +10030,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>417</v>
+        <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9963,13 +10087,13 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
@@ -9987,7 +10111,7 @@
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9995,10 +10119,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10006,10 +10130,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10021,13 +10145,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10078,13 +10202,13 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
@@ -10110,10 +10234,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10121,13 +10245,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>78</v>
@@ -10136,18 +10260,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10195,13 +10317,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10210,16 +10332,16 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>428</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10227,10 +10349,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10253,13 +10375,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>433</v>
+        <v>153</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>434</v>
+        <v>154</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10310,7 +10432,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>432</v>
+        <v>155</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10322,7 +10444,7 @@
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -10331,10 +10453,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>435</v>
+        <v>156</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10342,14 +10464,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10368,16 +10490,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>438</v>
+        <v>132</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>133</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>158</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>441</v>
+        <v>135</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10427,7 +10549,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>162</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10439,7 +10561,7 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -10448,10 +10570,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>442</v>
+        <v>156</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10459,43 +10581,45 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>444</v>
+        <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>445</v>
+        <v>228</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O75" t="s" s="2">
-        <v>447</v>
+        <v>141</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10544,19 +10668,19 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>230</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -10565,10 +10689,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>448</v>
+        <v>129</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10576,10 +10700,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10587,7 +10711,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>86</v>
@@ -10602,17 +10726,15 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10661,10 +10783,10 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>86</v>
@@ -10682,10 +10804,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10797,7 +10919,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10808,10 +10930,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10831,16 +10953,16 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10891,7 +11013,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10912,7 +11034,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10923,10 +11045,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10934,13 +11056,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>78</v>
@@ -10949,16 +11071,18 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11006,7 +11130,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11021,23 +11145,834 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AO79" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO79">
+  <autoFilter ref="A1:AO86">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11047,7 +11982,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1460,7 +1460,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1921,7 +1921,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="52.44140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -892,7 +892,7 @@
     <t>This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDentalDeviceStatus</t>
+    <t>http://va.gov/fhir/ValueSet/DentalDeviceStatus</t>
   </si>
   <si>
     <t>1355: target not supported</t>
@@ -1936,7 +1936,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.82421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file DENTAL DEVICE TRACKING (228.9) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file DENTAL DEVICE TRACKING (228.9) to us-core-implantable-device.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,7 +634,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1352: source value from DENTAL DEVICE TRACKING - IEN (228.9-.001)</t>
+    <t>1352: source value based on DENTAL DEVICE TRACKING - IEN (228.9-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -959,7 +959,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1370: source value from DENTAL DEVICE TRACKING - MANUFACTURER (228.9-4.1)</t>
+    <t>1370: source value based on DENTAL DEVICE TRACKING - MANUFACTURER (228.9-4.1)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceManufacturer</t>
@@ -1112,7 +1112,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1392: source value from DENTAL DEVICE TRACKING - MODEL (228.9-4.2)</t>
+    <t>1392: source value based on DENTAL DEVICE TRACKING - MODEL (228.9-4.2)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceModel</t>
@@ -1318,7 +1318,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1398: source value from DENTAL DEVICE TRACKING - TYPE (228.9-2)</t>
+    <t>1398: source value based on DENTAL DEVICE TRACKING - TYPE (228.9-2)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.DeviceType</t>
@@ -1473,7 +1473,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1403: reference from DENTAL DEVICE TRACKING - PATIENT (228.9-.03)</t>
+    <t>1403: reference based on DENTAL DEVICE TRACKING - PATIENT (228.9-.03)</t>
   </si>
   <si>
     <t>Dental.DeviceTracking.PatientIEN,Dental.DeviceTracking.PatientSID,Dental.DeviceTrackingDetail.PatientIEN</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3197" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -890,6 +890,9 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_DentalDeviceStatus](ConceptMap-VF-DentalDeviceStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/DentalDeviceStatus</t>
@@ -5532,9 +5535,11 @@
       <c r="X31" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y31" s="2"/>
+      <c r="Y31" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5567,16 +5572,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5584,10 +5589,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5613,10 +5618,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5646,10 +5651,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5667,7 +5672,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5691,7 +5696,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5699,14 +5704,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5728,13 +5733,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5784,7 +5789,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5799,27 +5804,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5845,10 +5850,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5899,7 +5904,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5914,13 +5919,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>238</v>
@@ -5931,10 +5936,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5957,13 +5962,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6014,7 +6019,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6029,27 +6034,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6072,13 +6077,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6129,7 +6134,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6144,27 +6149,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6190,10 +6195,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6244,7 +6249,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6259,27 +6264,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>238</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6305,13 +6310,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6361,7 +6366,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6376,13 +6381,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>238</v>
@@ -6393,10 +6398,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6422,10 +6427,10 @@
         <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6476,7 +6481,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6491,7 +6496,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6508,10 +6513,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6623,10 +6628,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6740,10 +6745,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6859,14 +6864,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6888,10 +6893,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6942,7 +6947,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6974,10 +6979,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7003,10 +7008,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7036,10 +7041,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7057,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -7078,7 +7083,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>238</v>
@@ -7089,10 +7094,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7118,10 +7123,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7172,7 +7177,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7187,13 +7192,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>238</v>
@@ -7204,10 +7209,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7233,13 +7238,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7289,7 +7294,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7310,7 +7315,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>238</v>
@@ -7321,10 +7326,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7350,10 +7355,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7383,10 +7388,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7404,7 +7409,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7436,10 +7441,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7551,10 +7556,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7668,10 +7673,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7694,19 +7699,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7755,7 +7760,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7776,7 +7781,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7787,10 +7792,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7902,10 +7907,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8019,10 +8024,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8048,16 +8053,16 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8067,7 +8072,7 @@
         <v>78</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>78</v>
@@ -8106,7 +8111,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8121,13 +8126,13 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8138,10 +8143,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8167,13 +8172,13 @@
         <v>152</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8223,7 +8228,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8244,7 +8249,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8255,10 +8260,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8284,14 +8289,14 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8301,7 +8306,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -8340,7 +8345,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8355,13 +8360,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8372,10 +8377,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8401,14 +8406,14 @@
         <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8418,7 +8423,7 @@
         <v>78</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>78</v>
@@ -8457,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8472,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8489,10 +8494,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8515,19 +8520,19 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8576,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8597,7 +8602,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8608,10 +8613,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8637,16 +8642,16 @@
         <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8695,7 +8700,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8710,13 +8715,13 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8727,10 +8732,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8756,10 +8761,10 @@
         <v>219</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8810,7 +8815,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8842,10 +8847,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8957,10 +8962,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9074,10 +9079,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9193,14 +9198,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9222,10 +9227,10 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9276,7 +9281,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -9308,10 +9313,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9337,10 +9342,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9391,7 +9396,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9423,10 +9428,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9452,10 +9457,10 @@
         <v>219</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9506,7 +9511,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9538,10 +9543,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9653,10 +9658,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9770,10 +9775,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9889,14 +9894,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9918,10 +9923,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9972,7 +9977,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10004,10 +10009,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10033,10 +10038,10 @@
         <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10087,7 +10092,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10119,10 +10124,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10148,10 +10153,10 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10202,7 +10207,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>86</v>
@@ -10234,10 +10239,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10263,10 +10268,10 @@
         <v>219</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10317,7 +10322,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10349,10 +10354,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10464,10 +10469,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10581,10 +10586,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10700,10 +10705,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10729,10 +10734,10 @@
         <v>174</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10783,7 +10788,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>86</v>
@@ -10815,10 +10820,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10841,13 +10846,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10898,7 +10903,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10930,10 +10935,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10959,10 +10964,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11013,7 +11018,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11045,10 +11050,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11071,17 +11076,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11130,7 +11135,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11145,16 +11150,16 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11162,10 +11167,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11191,10 +11196,10 @@
         <v>208</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11245,7 +11250,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11266,10 +11271,10 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -11277,10 +11282,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11303,16 +11308,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11362,7 +11367,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11383,10 +11388,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -11394,10 +11399,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11420,17 +11425,17 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11479,7 +11484,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11500,10 +11505,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -11511,10 +11516,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11540,13 +11545,13 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11596,7 +11601,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11617,10 +11622,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -11628,10 +11633,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11654,13 +11659,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11711,7 +11716,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11732,7 +11737,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11743,10 +11748,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11772,10 +11777,10 @@
         <v>174</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11826,7 +11831,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11858,10 +11863,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11884,13 +11889,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11941,7 +11946,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1060,9 +1060,6 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
-  </si>
-  <si>
-    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -6496,7 +6493,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6513,10 +6510,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6628,10 +6625,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6745,10 +6742,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6864,14 +6861,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6893,10 +6890,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6947,7 +6944,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6979,10 +6976,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7008,10 +7005,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7041,11 +7038,11 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7062,7 +7059,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -7083,7 +7080,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>238</v>
@@ -7094,10 +7091,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7123,10 +7120,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7177,7 +7174,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7192,13 +7189,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>238</v>
@@ -7209,10 +7206,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7238,10 +7235,10 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>325</v>
@@ -7294,7 +7291,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7326,10 +7323,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7355,10 +7352,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7388,11 +7385,11 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7409,7 +7406,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7441,10 +7438,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7556,10 +7553,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7673,10 +7670,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7699,19 +7696,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7760,7 +7757,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7781,7 +7778,7 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7792,10 +7789,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7907,10 +7904,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8024,10 +8021,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8053,16 +8050,16 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8072,46 +8069,46 @@
         <v>78</v>
       </c>
       <c r="S53" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8126,13 +8123,13 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8143,10 +8140,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8172,13 +8169,13 @@
         <v>152</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8228,7 +8225,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8249,7 +8246,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8260,10 +8257,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8289,14 +8286,14 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8306,46 +8303,46 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8360,13 +8357,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8377,10 +8374,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8406,14 +8403,14 @@
         <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8423,46 +8420,46 @@
         <v>78</v>
       </c>
       <c r="S56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8477,13 +8474,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8494,10 +8491,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8520,19 +8517,19 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8581,7 +8578,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8602,7 +8599,7 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8613,10 +8610,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8642,16 +8639,16 @@
         <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8700,7 +8697,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8715,13 +8712,13 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8732,10 +8729,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8761,10 +8758,10 @@
         <v>219</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8815,7 +8812,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8847,10 +8844,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8962,10 +8959,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9079,10 +9076,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9198,14 +9195,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9227,10 +9224,10 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9281,7 +9278,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -9313,10 +9310,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9342,10 +9339,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9396,7 +9393,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9428,10 +9425,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9457,10 +9454,10 @@
         <v>219</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9511,7 +9508,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9543,10 +9540,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9658,10 +9655,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9775,10 +9772,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9894,14 +9891,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9923,10 +9920,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9977,7 +9974,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10009,10 +10006,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10038,10 +10035,10 @@
         <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10092,7 +10089,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10124,10 +10121,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10153,10 +10150,10 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10207,7 +10204,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>86</v>
@@ -10239,10 +10236,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10268,10 +10265,10 @@
         <v>219</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10322,7 +10319,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10354,10 +10351,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10469,10 +10466,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10586,10 +10583,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10705,10 +10702,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10734,10 +10731,10 @@
         <v>174</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10788,7 +10785,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>86</v>
@@ -10820,10 +10817,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10846,13 +10843,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10903,7 +10900,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10935,10 +10932,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10964,10 +10961,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11018,7 +11015,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11050,10 +11047,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11076,17 +11073,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11135,7 +11132,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11150,16 +11147,16 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL79" t="s" s="2">
+      <c r="AM79" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11167,10 +11164,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11196,10 +11193,10 @@
         <v>208</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11250,7 +11247,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11271,10 +11268,10 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -11282,10 +11279,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11308,16 +11305,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11367,7 +11364,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11388,10 +11385,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -11399,10 +11396,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11425,17 +11422,17 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11484,7 +11481,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11505,10 +11502,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -11516,10 +11513,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11545,13 +11542,13 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11601,7 +11598,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11622,10 +11619,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -11633,10 +11630,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11659,13 +11656,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11716,7 +11713,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11737,7 +11734,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11748,10 +11745,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11777,10 +11774,10 @@
         <v>174</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11831,7 +11828,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11863,10 +11860,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11889,13 +11886,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11946,7 +11943,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDental.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDental.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
